--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-10-01</t>
+    <t>2024-11-05</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-01T00:00:00+00:00</t>
+    <t>2024-11-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41159</t>
+    <t>41241</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -73,19 +73,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du numérique en santé</t>
   </si>
   <si>
     <t>Description</t>
@@ -462,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -553,88 +541,72 @@
       <c r="A11" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>29</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -649,332 +621,332 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -989,13 +961,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1003,38 +975,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-11-05</t>
+    <t>2024-12-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T00:00:00+00:00</t>
+    <t>2024-12-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41241</t>
+    <t>41204</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-12-01</t>
+    <t>2025-01-02</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-03T00:00:00+00:00</t>
+    <t>2025-01-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41204</t>
+    <t>41154</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -31,25 +31,25 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-bdpm</t>
+    <t>https://smt.esante.gouv.fr/#terminologie-bdpm (use: secondary, )</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2025-01-02</t>
+    <t>2025-02-05</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Base_de_donn_es_publique_du_m_dicament___BDPM</t>
+    <t>BDPM</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Base de données publique du médicament - BDPM</t>
+    <t>Base de données publique du médicament</t>
   </si>
   <si>
     <t>Status</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-03T00:00:00+00:00</t>
+    <t>2025-02-10T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41154</t>
+    <t>41158</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-02-05</t>
+    <t>2025-03-04</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T00:00:00+00:00</t>
+    <t>2025-03-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41158</t>
+    <t>41199</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-03-04</t>
+    <t>2025-04-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T00:00:00+00:00</t>
+    <t>2025-04-02T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41199</t>
+    <t>41192</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="103">
   <si>
     <t>Property</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>Agence du numérique en santé</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -450,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -541,72 +547,80 @@
       <c r="A11" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" t="s" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>25</v>
       </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B19" t="s" s="2">
         <v>30</v>
       </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s" s="2">
         <v>33</v>
+      </c>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -621,332 +635,332 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -961,13 +975,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -975,38 +989,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-04-01</t>
+    <t>2025-05-05</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T00:00:00+00:00</t>
+    <t>2025-05-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41192</t>
+    <t>41165</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-05-05</t>
+    <t>2025-06-02</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T00:00:00+00:00</t>
+    <t>2025-06-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41165</t>
+    <t>41170</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-06-02</t>
+    <t>2025-07-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-03T00:00:00+00:00</t>
+    <t>2025-07-02T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41170</t>
+    <t>41109</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-07-01</t>
+    <t>2025-09-05</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-02T00:00:00+00:00</t>
+    <t>2025-09-05T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41109</t>
+    <t>41196</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-09-05</t>
+    <t>2025-10-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-05T00:00:00+00:00</t>
+    <t>2025-10-01T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41196</t>
+    <t>41118</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
   <si>
     <t>Property</t>
   </si>
@@ -85,12 +85,18 @@
     <t>Description</t>
   </si>
   <si>
+    <t>LA BDPM est un des référentiels du médicament gérée et distribuée par l’ANSM. Elle recense l’ensemble des spécialités et des présentations effectivement commercialisées durant les 5 dernières années. De ce fait, elle ne propose pas un historique exhaustif des codes de présentation et spécialités, celui-ci peut être obtenu grâce à la base RCP disponible sur le site de l’ANSM</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
     <t>Copyright</t>
   </si>
   <si>
+    <t>[LOv2](https://github.com/etalab/licence-ouverte/blob/master/LO.md)</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
@@ -112,7 +118,7 @@
     <t>Content</t>
   </si>
   <si>
-    <t>not-present</t>
+    <t>complete</t>
   </si>
   <si>
     <t>Supplements</t>
@@ -555,72 +561,76 @@
       <c r="A12" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -635,332 +645,332 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>22</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -975,13 +985,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -989,38 +999,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-10-01</t>
+    <t>2025-11-06</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-01T00:00:00+00:00</t>
+    <t>2025-11-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41118</t>
+    <t>41206</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-11-06</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-06T00:00:00+00:00</t>
+    <t>2025-12-02T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41206</t>
+    <t>41234</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-12-02</t>
+    <t>2025-12-03</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-02T00:00:00+00:00</t>
+    <t>2025-12-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41234</t>
+    <t>41229</t>
   </si>
   <si>
     <t>Code</t>
@@ -146,18 +146,6 @@
   </si>
   <si>
     <t>code</t>
-  </si>
-  <si>
-    <t>etat_commercialisation</t>
-  </si>
-  <si>
-    <t>http://www.data.esante.gouv.fr/ANSM/BDPM-core-ontology/etat_commercialisation</t>
-  </si>
-  <si>
-    <t>statut_CIP</t>
-  </si>
-  <si>
-    <t>http://www.data.esante.gouv.fr/ANSM/BDPM-core-ontology/statut_CIP</t>
   </si>
   <si>
     <t>date_commercialisation</t>
@@ -640,7 +628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -678,43 +666,43 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +714,7 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -738,31 +726,31 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -774,7 +762,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -798,7 +786,7 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -810,7 +798,7 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -822,7 +810,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -834,7 +822,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -846,7 +834,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -870,7 +858,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -882,7 +870,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
@@ -894,7 +882,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22">
@@ -904,73 +892,49 @@
       <c r="B22" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>90</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>90</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>43</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="B25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -991,7 +955,7 @@
         <v>22</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -999,38 +963,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-12-03</t>
+    <t>2026-01-06</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T00:00:00+00:00</t>
+    <t>2026-01-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41229</t>
+    <t>41107</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-01-06</t>
+    <t>2026-02-03</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T00:00:00+00:00</t>
+    <t>2026-02-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41107</t>
+    <t>41142</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-02-03</t>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T00:00:00+00:00</t>
+    <t>2026-03-03T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41142</t>
+    <t>41219</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-04-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T00:00:00+00:00</t>
+    <t>2026-04-01T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41219</t>
+    <t>41228</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-04-01</t>
+    <t>2026-05-05</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T00:00:00+00:00</t>
+    <t>2026-05-05T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41228</t>
+    <t>41281</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/main/CodeSystem-terminologie-bdpm.xlsx
+++ b/ig/main/CodeSystem-terminologie-bdpm.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026-05-05</t>
+    <t>2026-06-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T00:00:00+00:00</t>
+    <t>2026-06-01T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41281</t>
+    <t>41218</t>
   </si>
   <si>
     <t>Code</t>
